--- a/data/metadata/diccionario_saber11.xlsx
+++ b/data/metadata/diccionario_saber11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\OneDrive - Universidad del Magdalena\Documentos\Project_DataIcfes\data\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D22339-EE2B-4716-A229-C22AF806A929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE5D883-9220-4E58-B94B-C96E4FA0F65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
   <si>
     <t>nombre_final</t>
   </si>
@@ -92,6 +92,48 @@
   </si>
   <si>
     <t>recaf_punt_c_naturales</t>
+  </si>
+  <si>
+    <t>Trazabilidad interna; descartada como llave de vinculación exacta (ver bitácora de decisiones y guía metodológica oficial del ICFES sobre cruces)</t>
+  </si>
+  <si>
+    <t>Componente de refuerzo de la llave de vinculación</t>
+  </si>
+  <si>
+    <t>Núcleo de la llave de vinculación</t>
+  </si>
+  <si>
+    <t>Se usa el código DANE (no el nombre de ciudad) para evitar pérdida de ceros a la izquierda; componente de la llave</t>
+  </si>
+  <si>
+    <t>Componente de la llave, verificado empíricamente que reduce colisiones</t>
+  </si>
+  <si>
+    <t>Colegio de origen; componente de la llave</t>
+  </si>
+  <si>
+    <t>Variable descontinuada a partir de 2014-2</t>
+  </si>
+  <si>
+    <t>Nombre usado antes de la reforma de 2014-2</t>
+  </si>
+  <si>
+    <t>Nombre vigente desde la reforma de 2014-2</t>
+  </si>
+  <si>
+    <t>Nombre usado antes de la reforma de 2014-2 (antes llamado Lenguaje)</t>
+  </si>
+  <si>
+    <t>Puntaje recalificado con metodología nueva, disponible incluso antes de la reforma</t>
+  </si>
+  <si>
+    <t>No existe antes de 2014-2 (variable introducida con la reforma)</t>
+  </si>
+  <si>
+    <t>Rango documentado por el diccionario oficial; disponibilidad real puede variar por archivo, verificar en el log</t>
+  </si>
+  <si>
+    <t>nota</t>
   </si>
 </sst>
 </file>
@@ -135,9 +177,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,15 +493,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,271 +515,325 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="E1" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>20101</v>
-      </c>
-      <c r="D2">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C2" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D2" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>20101</v>
-      </c>
-      <c r="D3">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C3" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D3" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4">
-        <v>20101</v>
-      </c>
-      <c r="D4">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="C4" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D4" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
-        <v>20101</v>
-      </c>
-      <c r="D5">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="C5" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>20101</v>
-      </c>
-      <c r="D6">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="C6" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D6" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7">
-        <v>20101</v>
-      </c>
-      <c r="D7">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="C7" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D7" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8">
-        <v>20101</v>
-      </c>
-      <c r="D8">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="C8" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D8" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9">
-        <v>20101</v>
-      </c>
-      <c r="D9">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="C9" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D9" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10">
-        <v>20101</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D10" s="4">
         <v>20141</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="E10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C11">
-        <v>20101</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D11" s="4">
         <v>20141</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="E11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>20142</v>
       </c>
-      <c r="D12">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="D12" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C13">
-        <v>20101</v>
-      </c>
-      <c r="D13">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="C13" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D13" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14">
-        <v>20101</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D14" s="4">
         <v>20141</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="E14" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>20142</v>
       </c>
-      <c r="D15">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="D15" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C16">
-        <v>20101</v>
-      </c>
-      <c r="D16">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="C16" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D16" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C17">
-        <v>20101</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="4">
+        <v>20101</v>
+      </c>
+      <c r="D17" s="4">
         <v>20141</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="E17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="4">
         <v>20142</v>
       </c>
-      <c r="D18">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="D18" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C19">
-        <v>20101</v>
-      </c>
-      <c r="D19">
-        <v>20252</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="C19" s="4">
+        <v>20142</v>
+      </c>
+      <c r="D19" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="4">
         <v>20142</v>
       </c>
-      <c r="D20">
-        <v>20252</v>
+      <c r="D20" s="4">
+        <v>20252</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata/diccionario_saber11.xlsx
+++ b/data/metadata/diccionario_saber11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\OneDrive - Universidad del Magdalena\Documentos\Project_DataIcfes\data\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE5D883-9220-4E58-B94B-C96E4FA0F65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80340DE8-3464-447E-9B12-141FC7C4188A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>nombre_final</t>
   </si>
@@ -52,12 +52,24 @@
     <t>estu_mcpio_reside</t>
   </si>
   <si>
+    <t>estu_depto_reside</t>
+  </si>
+  <si>
     <t>fami_estratovivienda</t>
   </si>
   <si>
     <t>cole_cod_dane_establecimiento</t>
   </si>
   <si>
+    <t>cole_nombre_establecimiento</t>
+  </si>
+  <si>
+    <t>cole_naturaleza</t>
+  </si>
+  <si>
+    <t>cole_jornada</t>
+  </si>
+  <si>
     <t>fami_nivelsisben</t>
   </si>
   <si>
@@ -82,7 +94,7 @@
     <t>percentil_global</t>
   </si>
   <si>
-    <t>estu_cod_reside_mcpio</t>
+    <t>fami_ingreso_familiar_mensual</t>
   </si>
   <si>
     <t>punt_ciencias_sociales</t>
@@ -94,62 +106,30 @@
     <t>recaf_punt_c_naturales</t>
   </si>
   <si>
-    <t>Trazabilidad interna; descartada como llave de vinculación exacta (ver bitácora de decisiones y guía metodológica oficial del ICFES sobre cruces)</t>
-  </si>
-  <si>
-    <t>Componente de refuerzo de la llave de vinculación</t>
-  </si>
-  <si>
-    <t>Núcleo de la llave de vinculación</t>
-  </si>
-  <si>
-    <t>Se usa el código DANE (no el nombre de ciudad) para evitar pérdida de ceros a la izquierda; componente de la llave</t>
-  </si>
-  <si>
-    <t>Componente de la llave, verificado empíricamente que reduce colisiones</t>
-  </si>
-  <si>
-    <t>Colegio de origen; componente de la llave</t>
-  </si>
-  <si>
-    <t>Variable descontinuada a partir de 2014-2</t>
-  </si>
-  <si>
-    <t>Nombre usado antes de la reforma de 2014-2</t>
-  </si>
-  <si>
-    <t>Nombre vigente desde la reforma de 2014-2</t>
-  </si>
-  <si>
-    <t>Nombre usado antes de la reforma de 2014-2 (antes llamado Lenguaje)</t>
-  </si>
-  <si>
-    <t>Puntaje recalificado con metodología nueva, disponible incluso antes de la reforma</t>
-  </si>
-  <si>
-    <t>No existe antes de 2014-2 (variable introducida con la reforma)</t>
-  </si>
-  <si>
-    <t>Rango documentado por el diccionario oficial; disponibilidad real puede variar por archivo, verificar en el log</t>
-  </si>
-  <si>
-    <t>nota</t>
+    <t>estu_trabajaactualmente</t>
+  </si>
+  <si>
+    <t>fami_ingresofmiliarmensual</t>
+  </si>
+  <si>
+    <t>estu_trabaja_actualmente</t>
+  </si>
+  <si>
+    <t>estu_tipocarreradeseada</t>
+  </si>
+  <si>
+    <t>estu_mcpio_presentacion</t>
+  </si>
+  <si>
+    <t>estu_cod_mcpio_presentacion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -177,18 +157,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,347 +463,418 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D2" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2">
+        <v>20101</v>
+      </c>
+      <c r="D2">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>20101</v>
+      </c>
+      <c r="D3">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>20101</v>
+      </c>
+      <c r="D4">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>20101</v>
+      </c>
+      <c r="D5">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>20101</v>
+      </c>
+      <c r="D6">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>20101</v>
+      </c>
+      <c r="D7">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>20101</v>
+      </c>
+      <c r="D8">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>20101</v>
+      </c>
+      <c r="D9">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>20101</v>
+      </c>
+      <c r="D10">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>20101</v>
+      </c>
+      <c r="D11">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>20101</v>
+      </c>
+      <c r="D12">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>20101</v>
+      </c>
+      <c r="D13">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>20101</v>
+      </c>
+      <c r="D14">
+        <v>20141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>20101</v>
+      </c>
+      <c r="D15">
+        <v>20141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>20142</v>
+      </c>
+      <c r="D16">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17">
+        <v>20101</v>
+      </c>
+      <c r="D17">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18">
+        <v>20101</v>
+      </c>
+      <c r="D18">
+        <v>20141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19">
+        <v>20142</v>
+      </c>
+      <c r="D19">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>20101</v>
+      </c>
+      <c r="D20">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>20101</v>
+      </c>
+      <c r="D21">
+        <v>20141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>20142</v>
+      </c>
+      <c r="D22">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>20101</v>
+      </c>
+      <c r="D23">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>20142</v>
+      </c>
+      <c r="D24">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25">
+        <v>20101</v>
+      </c>
+      <c r="D25">
+        <v>20142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D3" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D4" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D5" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D6" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D7" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D8" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D9" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="B26" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D10" s="4">
-        <v>20141</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D11" s="4">
-        <v>20141</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C26">
+        <v>20101</v>
+      </c>
+      <c r="D26">
+        <v>20142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <v>20101</v>
+      </c>
+      <c r="D27">
         <v>20142</v>
       </c>
-      <c r="D12" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E12" s="2" t="s">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <v>20101</v>
+      </c>
+      <c r="D28">
+        <v>20142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D13" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D14" s="4">
-        <v>20141</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29">
+        <v>20101</v>
+      </c>
+      <c r="D29">
         <v>20142</v>
-      </c>
-      <c r="D15" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D16" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4">
-        <v>20101</v>
-      </c>
-      <c r="D17" s="4">
-        <v>20141</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="4">
-        <v>20142</v>
-      </c>
-      <c r="D18" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="4">
-        <v>20142</v>
-      </c>
-      <c r="D19" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="4">
-        <v>20142</v>
-      </c>
-      <c r="D20" s="4">
-        <v>20252</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata/diccionario_saber11.xlsx
+++ b/data/metadata/diccionario_saber11.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\OneDrive - Universidad del Magdalena\Documentos\Project_DataIcfes\data\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80340DE8-3464-447E-9B12-141FC7C4188A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97577007-02AA-4827-85AA-F3BF28158151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="homologacion" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">homologacion!$A$1:$D$31</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
   <si>
     <t>nombre_final</t>
   </si>
@@ -122,6 +125,12 @@
   </si>
   <si>
     <t>estu_cod_mcpio_presentacion</t>
+  </si>
+  <si>
+    <t>estu_cod_reside_mcpio</t>
+  </si>
+  <si>
+    <t>estu_cod_reside_depto</t>
   </si>
 </sst>
 </file>
@@ -463,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -874,10 +883,39 @@
         <v>20101</v>
       </c>
       <c r="D29">
-        <v>20142</v>
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30">
+        <v>20101</v>
+      </c>
+      <c r="D30">
+        <v>20252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31">
+        <v>20101</v>
+      </c>
+      <c r="D31">
+        <v>20252</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>